--- a/data/normalized/basidiospore.xlsx
+++ b/data/normalized/basidiospore.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hensley/Desktop/wiscam_microscopy/data/normalized/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{267F596A-9EEB-CB40-8A2C-FE4D3EEEB04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3D2CC4-57AA-604C-9A84-E6AFDD544CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-33300" yWindow="-1320" windowWidth="27640" windowHeight="16640" xr2:uid="{8188D9C6-D56A-8E47-B77A-6198909A1C26}"/>
   </bookViews>
@@ -812,45 +812,6 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2">
-        <v>25</v>
-      </c>
-      <c r="E2">
-        <v>7.5</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>12</v>
-      </c>
-      <c r="H2">
-        <v>14.5</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
-      <c r="K2">
-        <v>12</v>
-      </c>
-      <c r="L2">
-        <v>12</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>1.5</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -861,45 +822,6 @@
       </c>
       <c r="C3" t="s">
         <v>14</v>
-      </c>
-      <c r="D3">
-        <v>25</v>
-      </c>
-      <c r="E3">
-        <v>8</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>11.5</v>
-      </c>
-      <c r="H3">
-        <v>12</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>10</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>1.2</v>
-      </c>
-      <c r="O3">
-        <v>1.5</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">

--- a/data/normalized/basidiospore.xlsx
+++ b/data/normalized/basidiospore.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hensley/Desktop/wiscam_microscopy/data/normalized/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3D2CC4-57AA-604C-9A84-E6AFDD544CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634BCD7B-42F5-CA4C-8B41-D56A4DCF47E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-33300" yWindow="-1320" windowWidth="27640" windowHeight="16640" xr2:uid="{8188D9C6-D56A-8E47-B77A-6198909A1C26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="97">
   <si>
     <t>species</t>
   </si>
@@ -321,6 +321,12 @@
   </si>
   <si>
     <t>shape</t>
+  </si>
+  <si>
+    <t>Amanita firma</t>
+  </si>
+  <si>
+    <t>Amanita banningiana</t>
   </si>
 </sst>
 </file>
@@ -743,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C01937D-C4BF-1646-B06C-D438550473A7}">
-  <dimension ref="A1:Q145"/>
+  <dimension ref="A1:Q147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1981,65 +1987,65 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109">
+        <v>30295</v>
+      </c>
+      <c r="B109" t="s">
+        <v>96</v>
+      </c>
+      <c r="C109" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>30300</v>
+      </c>
+      <c r="B110" t="s">
+        <v>95</v>
+      </c>
+      <c r="C110" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111">
         <v>40220</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B111" t="s">
         <v>70</v>
       </c>
-      <c r="C109" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>16</v>
-      </c>
-      <c r="B110" t="s">
-        <v>52</v>
-      </c>
-      <c r="C110" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>17</v>
-      </c>
-      <c r="B111" t="s">
-        <v>52</v>
-      </c>
       <c r="C111" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B112" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C112" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C113" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B114" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C114" t="s">
         <v>55</v>
@@ -2047,29 +2053,29 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B115" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C115" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B116" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C116" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B117" t="s">
         <v>66</v>
@@ -2080,7 +2086,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B118" t="s">
         <v>66</v>
@@ -2091,7 +2097,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B119" t="s">
         <v>66</v>
@@ -2102,7 +2108,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B120" t="s">
         <v>66</v>
@@ -2113,40 +2119,40 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B121" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C121" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>28</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>75</v>
+        <v>26</v>
+      </c>
+      <c r="B122" t="s">
+        <v>66</v>
       </c>
       <c r="C122" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>29</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>75</v>
+        <v>27</v>
+      </c>
+      <c r="B123" t="s">
+        <v>70</v>
       </c>
       <c r="C123" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>75</v>
@@ -2157,10 +2163,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>31</v>
-      </c>
-      <c r="B125" t="s">
-        <v>77</v>
+        <v>29</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="C125" t="s">
         <v>60</v>
@@ -2168,29 +2174,29 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>32</v>
-      </c>
-      <c r="B126" t="s">
-        <v>78</v>
+        <v>30</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="C126" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B127" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C127" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B128" t="s">
         <v>78</v>
@@ -2201,7 +2207,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B129" t="s">
         <v>78</v>
@@ -2212,7 +2218,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B130" t="s">
         <v>78</v>
@@ -2223,7 +2229,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B131" t="s">
         <v>78</v>
@@ -2234,7 +2240,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B132" t="s">
         <v>78</v>
@@ -2245,65 +2251,65 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B133" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C133" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B134" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C134" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B135" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C135" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B136" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C136" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B137" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C137" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B138" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C138" t="s">
         <v>55</v>
@@ -2311,18 +2317,18 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B139" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C139" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B140" t="s">
         <v>76</v>
@@ -2333,7 +2339,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B141" t="s">
         <v>76</v>
@@ -2344,7 +2350,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B142" t="s">
         <v>76</v>
@@ -2355,7 +2361,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B143" t="s">
         <v>76</v>
@@ -2364,8 +2370,30 @@
         <v>55</v>
       </c>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>48</v>
+      </c>
+      <c r="B144" t="s">
+        <v>76</v>
+      </c>
+      <c r="C144" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>49</v>
+      </c>
       <c r="B145" t="s">
+        <v>76</v>
+      </c>
+      <c r="C145" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B147" t="s">
         <v>92</v>
       </c>
     </row>
